--- a/小野町_引継ぎ_整理済/14_アンケート集計/小野町_令和7年度調査_集計データ整理_20260805.xlsx
+++ b/小野町_引継ぎ_整理済/14_アンケート集計/小野町_令和7年度調査_集計データ整理_20260805.xlsx
@@ -21,7 +21,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'00_調査概要_対象と回収'!$A$1:$G$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'01_リスク分析_10項目'!$A$1:$L$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'02_リスク分析_年齢階層別'!$A$1:$H$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'03_ニーズ調査_主要結果'!$A$1:$E$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'03_ニーズ調査_主要結果'!$A$1:$E$44</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'04_在宅介護実態調査_主要結果'!$A$1:$E$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'05_クロス集計_実施可否'!$A$1:$E$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'06_妥当性検証'!$A$1:$E$12</definedName>
@@ -1989,7 +1989,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:E44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2871,12 +2871,12 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>参加の条件：介護予防に効果があること</t>
+          <t>参加の条件：介護予防に効果があると感じられること</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>43.1％</t>
+          <t>48.3％</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
@@ -2898,12 +2898,12 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>参加の条件：友人・仲間が一緒に参加すること</t>
+          <t>参加の条件：何をするのか事前に分かりやすく説明されていること</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>30.0％</t>
+          <t>43.1％</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>心がけていること：自分で自分のことをする</t>
+          <t>参加の条件：友人・仲間が一緒に参加すること</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>82.9％</t>
+          <t>30.0％</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
@@ -2940,24 +2940,24 @@
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>同上</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>生活課題</t>
+          <t>介護予防</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>日常生活で困っていること：家の周りの草刈り等</t>
+          <t>心がけていること：自分で自分のことをする</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>18.7％</t>
+          <t>82.9％</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
@@ -2967,7 +2967,7 @@
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>生活支援体制整備事業の対象</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -2979,12 +2979,12 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>通院・買い物で「移動手段がない」</t>
+          <t>日常生活で困っていること：家の周りの草刈り等</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>4.9％</t>
+          <t>18.7％</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>生活支援体制整備事業の対象</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>通院・買い物で「困っていることはない」</t>
+          <t>通院・買い物で「移動手段がない」</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>72.1％</t>
+          <t>4.9％</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
@@ -3028,17 +3028,17 @@
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>たすけあい</t>
+          <t>生活課題</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>病気のとき看病や世話をしてくれる人がいない</t>
+          <t>通院・買い物で「困っていることはない」</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>5.5％</t>
+          <t>72.1％</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>見守り体制</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -3060,12 +3060,12 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>家族・友人以外に相談する人がいない</t>
+          <t>病気のとき看病や世話をしてくれる人がいない</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>38.0％</t>
+          <t>5.5％</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>相談体制</t>
+          <t>見守り体制</t>
         </is>
       </c>
     </row>
@@ -3087,12 +3087,12 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>友人・知人と会う頻度が「ほとんどない」</t>
+          <t>家族・友人以外に相談する人がいない</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>11.8％</t>
+          <t>38.0％</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
@@ -3102,24 +3102,24 @@
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>孤立の指標</t>
+          <t>相談体制</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="10" t="inlineStr">
         <is>
-          <t>災害</t>
+          <t>たすけあい</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>**災害時に一人で避難できない**</t>
+          <t>友人・知人と会う頻度が「ほとんどない」</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>**14.2％**</t>
+          <t>11.8％</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
@@ -3129,7 +3129,7 @@
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>**個別避難計画の対象規模。高齢者人口3,483人に換算すると約495人**</t>
+          <t>孤立の指標</t>
         </is>
       </c>
     </row>
@@ -3141,27 +3141,54 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
+          <t>**災害時に一人で避難できない**</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>**14.2％**</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>**個別避難計画の対象規模。高齢者人口3,483人に換算すると約495人**</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="10" t="inlineStr">
+        <is>
+          <t>災害</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
           <t>災害時に助けてくれる人が「いない」</t>
         </is>
       </c>
-      <c r="C43" s="6" t="inlineStr">
+      <c r="C44" s="6" t="inlineStr">
         <is>
           <t>11.3％</t>
         </is>
       </c>
-      <c r="D43" s="5" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="E43" s="6" t="inlineStr">
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E43"/>
+  <autoFilter ref="A1:E44"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5545,7 +5572,7 @@
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>「参加していない」76.2％の内訳を尋ねる設問がない。代替として介護予防事業への参加条件（開催場所・時間63.7％、料金53.4％、効果43.1％、友人と一緒30.0％）がある</t>
+          <t>「参加していない」76.2％の内訳を尋ねる設問がない。代替として介護予防事業への参加条件（開催場所・時間63.7％、料金53.4％、効果48.3％、事前説明43.1％、友人と一緒30.0％）がある</t>
         </is>
       </c>
       <c r="E3" s="6" t="inlineStr">
@@ -6609,7 +6636,7 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>**地域活動に参加者として参加する意向は50.9％あるが、企画・運営者としては32.0％にとどまり、参加したくないが54.8％。**参加の条件は開催場所・時間63.7％、料金53.4％、効果43.1％、友人と一緒30.0％</t>
+          <t>**地域活動に参加者として参加する意向は50.9％あるが、企画・運営者としては32.0％にとどまり、参加したくないが54.8％。**参加の条件は開催場所・時間63.7％、料金53.4％、効果48.3％、友人と一緒30.0％</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
